--- a/accountant-skill/data/Jan2026/purchases_journal.xlsx
+++ b/accountant-skill/data/Jan2026/purchases_journal.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Purchases Journal" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchases Journal" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -520,10 +520,10 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>320000</v>
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>185000</v>
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5020</v>
+        <v>50100</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>95000</v>
@@ -643,10 +643,10 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>145000</v>
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>265000</v>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5020</v>
+        <v>50100</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>72000</v>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>198000</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>223000</v>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>310000</v>
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5020</v>
+        <v>50100</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>58000</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5420</v>
+        <v>65000</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>45000</v>
